--- a/backend/fixtures/orders_dummy.xlsx
+++ b/backend/fixtures/orders_dummy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>FG Description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Connection Status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Real Status (PPC)</t>
         </is>
@@ -466,15 +471,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Stand-up pouch 500g, matte, zipper</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Shree Packaging Pvt Ltd</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>CONN-PLANT-A-OK</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>In Production</t>
         </is>
@@ -498,15 +508,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Stand-up pouch 1kg, gloss</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Shree Packaging Pvt Ltd</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>CONN-PLANT-A-OK</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Dispatched</t>
         </is>
@@ -530,15 +545,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Spice pouch 200g, matte</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Mehta Foods</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>CONN-PLANT-B-OK</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Ready for Dispatch</t>
         </is>
@@ -562,15 +582,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Spice pouch 500g, gloss</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Mehta Foods</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>CONN-PLANT-B-OK</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Printing</t>
         </is>
@@ -594,15 +619,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Namkeen pouch 1kg, metallised</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Mehta Foods</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>CONN-PLANT-B-DELAY</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Awaiting Material</t>
         </is>
@@ -626,15 +656,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Shrink sleeve, 500ml bottle</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Gujarat Polymers</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>CONN-PLANT-A-OK</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Lamination</t>
         </is>
@@ -658,15 +693,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Shrink sleeve, 1L bottle</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Gujarat Polymers</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>CONN-PLANT-A-OK</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Slitting</t>
         </is>
@@ -690,15 +730,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Fertiliser bag 5kg, BOPP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Patel Agro Industries </t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>CONN-PLANT-C-OK</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Cylinder Making</t>
         </is>
@@ -722,15 +767,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Tablet strip label, 40x60mm</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>SUNRISE PHARMA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>CONN-PLANT-C-OK</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Quality Check</t>
         </is>
@@ -754,15 +804,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Garment label roll, satin</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Royal Textiles</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>CONN-PLANT-B-OK</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
